--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 02:32</t>
+          <t>更新时间: 2026-09-15 10:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 10:02</t>
+          <t>更新时间: 2026-09-15 12:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 12:52</t>
+          <t>更新时间: 2026-09-15 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:34</t>
+          <t>更新时间: 2026-09-15 15:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 15:53</t>
+          <t>更新时间: 2026-09-15 17:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 17:14</t>
+          <t>更新时间: 2026-09-16 09:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:49</t>
+          <t>更新时间: 2026-09-16 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 12:47</t>
+          <t>更新时间: 2026-09-16 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:27</t>
+          <t>更新时间: 2026-09-16 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 15:46</t>
+          <t>更新时间: 2026-09-16 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 17:07</t>
+          <t>更新时间: 2026-09-17 09:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:51</t>
+          <t>更新时间: 2026-09-17 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 12:51</t>
+          <t>更新时间: 2026-09-17 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:35</t>
+          <t>更新时间: 2026-09-17 15:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 15:49</t>
+          <t>更新时间: 2026-09-17 17:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 17:15</t>
+          <t>更新时间: 2026-09-18 09:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:45</t>
+          <t>更新时间: 2026-09-18 12:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:41</t>
+          <t>更新时间: 2026-09-18 13:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:23</t>
+          <t>更新时间: 2026-09-18 15:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 15:29</t>
+          <t>更新时间: 2026-09-18 16:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 16:49</t>
+          <t>更新时间: 2026-09-19 09:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:46</t>
+          <t>更新时间: 2026-09-19 12:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:36</t>
+          <t>更新时间: 2026-09-19 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:16</t>
+          <t>更新时间: 2026-09-19 15:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 15:24</t>
+          <t>更新时间: 2026-09-19 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 16:35</t>
+          <t>更新时间: 2026-09-20 09:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:50</t>
+          <t>更新时间: 2026-09-20 12:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:52</t>
+          <t>更新时间: 2026-09-20 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:31</t>
+          <t>更新时间: 2026-09-20 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 15:48</t>
+          <t>更新时间: 2026-09-20 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 17:07</t>
+          <t>更新时间: 2026-09-21 09:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:40</t>
+          <t>更新时间: 2026-09-21 12:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 12:53</t>
+          <t>更新时间: 2026-09-21 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:38</t>
+          <t>更新时间: 2026-09-21 16:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 16:02</t>
+          <t>更新时间: 2026-09-21 17:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 17:40</t>
+          <t>更新时间: 2026-09-22 10:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 10:03</t>
+          <t>更新时间: 2026-09-22 12:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 12:53</t>
+          <t>更新时间: 2026-09-22 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:35</t>
+          <t>更新时间: 2026-09-22 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 15:48</t>
+          <t>更新时间: 2026-09-22 17:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 17:05</t>
+          <t>更新时间: 2026-09-23 09:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:55</t>
+          <t>更新时间: 2026-09-23 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 12:43</t>
+          <t>更新时间: 2026-09-23 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:22</t>
+          <t>更新时间: 2026-09-23 15:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 15:50</t>
+          <t>更新时间: 2026-09-23 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 17:07</t>
+          <t>更新时间: 2026-09-24 09:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:51</t>
+          <t>更新时间: 2026-09-24 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:48</t>
+          <t>更新时间: 2026-09-24 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:38</t>
+          <t>更新时间: 2026-09-24 15:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 15:40</t>
+          <t>更新时间: 2026-09-24 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 17:02</t>
+          <t>更新时间: 2026-09-25 10:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 10:02</t>
+          <t>更新时间: 2026-09-25 12:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 12:55</t>
+          <t>更新时间: 2026-09-25 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:34</t>
+          <t>更新时间: 2026-09-25 15:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 15:58</t>
+          <t>更新时间: 2026-09-25 17:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 17:25</t>
+          <t>更新时间: 2026-09-26 10:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 10:05</t>
+          <t>更新时间: 2026-09-26 12:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 12:56</t>
+          <t>更新时间: 2026-09-26 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:41</t>
+          <t>更新时间: 2026-09-26 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 15:51</t>
+          <t>更新时间: 2026-09-26 17:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 17:11</t>
+          <t>更新时间: 2026-09-27 09:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:58</t>
+          <t>更新时间: 2026-09-27 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:16</t>
+          <t>更新时间: 2026-09-27 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:58</t>
+          <t>更新时间: 2026-09-27 16:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 16:22</t>
+          <t>更新时间: 2026-09-27 17:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 17:51</t>
+          <t>更新时间: 2026-09-28 10:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 10:10</t>
+          <t>更新时间: 2026-09-28 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 13:21</t>
+          <t>更新时间: 2026-09-28 14:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:06</t>
+          <t>更新时间: 2026-09-28 16:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 16:48</t>
+          <t>更新时间: 2026-09-28 18:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 18:38</t>
+          <t>更新时间: 2026-09-29 10:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:54</t>
+          <t>更新时间: 2026-09-29 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 13:42</t>
+          <t>更新时间: 2026-09-29 14:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:23</t>
+          <t>更新时间: 2026-09-29 16:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 16:43</t>
+          <t>更新时间: 2026-09-29 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 18:26</t>
+          <t>更新时间: 2026-09-30 10:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:35</t>
+          <t>更新时间: 2026-09-30 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 13:30</t>
+          <t>更新时间: 2026-09-30 14:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:08</t>
+          <t>更新时间: 2026-09-30 16:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 16:44</t>
+          <t>更新时间: 2026-09-30 18:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 18:19</t>
+          <t>更新时间: 2026-10-01 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:36</t>
+          <t>更新时间: 2026-10-01 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 13:50</t>
+          <t>更新时间: 2026-10-01 14:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 14:40</t>
+          <t>更新时间: 2026-10-01 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 17:06</t>
+          <t>更新时间: 2026-10-01 18:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 18:45</t>
+          <t>更新时间: 2026-10-02 10:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:44</t>
+          <t>更新时间: 2026-10-02 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 13:34</t>
+          <t>更新时间: 2026-10-02 14:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:25</t>
+          <t>更新时间: 2026-10-02 16:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 16:40</t>
+          <t>更新时间: 2026-10-02 18:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 18:20</t>
+          <t>更新时间: 2026-10-03 10:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:35</t>
+          <t>更新时间: 2026-10-03 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:16</t>
+          <t>更新时间: 2026-10-03 13:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:53</t>
+          <t>更新时间: 2026-10-03 16:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:19</t>
+          <t>更新时间: 2026-10-03 17:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 17:42</t>
+          <t>更新时间: 2026-10-04 11:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 11:04</t>
+          <t>更新时间: 2026-10-04 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:50</t>
+          <t>更新时间: 2026-10-04 14:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:30</t>
+          <t>更新时间: 2026-10-04 16:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 16:33</t>
+          <t>更新时间: 2026-10-04 18:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 18:25</t>
+          <t>更新时间: 2026-10-05 10:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 10:30</t>
+          <t>更新时间: 2026-10-05 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 13:36</t>
+          <t>更新时间: 2026-10-05 14:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:24</t>
+          <t>更新时间: 2026-10-05 17:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 17:15</t>
+          <t>更新时间: 2026-10-05 19:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 19:13</t>
+          <t>更新时间: 2026-10-06 11:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 11:33</t>
+          <t>更新时间: 2026-10-06 14:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:18</t>
+          <t>更新时间: 2026-10-06 15:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:00</t>
+          <t>更新时间: 2026-10-06 17:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 17:08</t>
+          <t>更新时间: 2026-10-06 19:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 19:03</t>
+          <t>更新时间: 2026-10-07 10:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 10:57</t>
+          <t>更新时间: 2026-10-07 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 13:57</t>
+          <t>更新时间: 2026-10-07 14:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:41</t>
+          <t>更新时间: 2026-10-07 16:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 16:54</t>
+          <t>更新时间: 2026-10-07 18:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 18:52</t>
+          <t>更新时间: 2026-10-08 11:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 11:05</t>
+          <t>更新时间: 2026-10-08 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:01</t>
+          <t>更新时间: 2026-10-08 14:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:48</t>
+          <t>更新时间: 2026-10-08 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 17:10</t>
+          <t>更新时间: 2026-10-08 19:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 19:10</t>
+          <t>更新时间: 2026-10-09 11:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 11:19</t>
+          <t>更新时间: 2026-10-09 14:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:06</t>
+          <t>更新时间: 2026-10-09 14:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:56</t>
+          <t>更新时间: 2026-10-09 17:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 17:19</t>
+          <t>更新时间: 2026-10-09 19:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 19:09</t>
+          <t>更新时间: 2026-10-10 10:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 10:50</t>
+          <t>更新时间: 2026-10-10 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 13:50</t>
+          <t>更新时间: 2026-10-10 14:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:31</t>
+          <t>更新时间: 2026-10-10 16:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 16:40</t>
+          <t>更新时间: 2026-10-10 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 18:26</t>
+          <t>更新时间: 2026-10-11 10:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 10:22</t>
+          <t>更新时间: 2026-10-11 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 13:44</t>
+          <t>更新时间: 2026-10-11 14:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:36</t>
+          <t>更新时间: 2026-10-11 17:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 17:04</t>
+          <t>更新时间: 2026-10-11 18:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 18:38</t>
+          <t>更新时间: 2026-10-12 10:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 10:50</t>
+          <t>更新时间: 2026-10-12 13:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 13:54</t>
+          <t>更新时间: 2026-10-12 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:44</t>
+          <t>更新时间: 2026-10-12 17:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 17:26</t>
+          <t>更新时间: 2026-10-12 19:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 19:41</t>
+          <t>更新时间: 2026-10-13 11:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 11:59</t>
+          <t>更新时间: 2026-10-13 14:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 14:45</t>
+          <t>更新时间: 2026-10-13 15:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:12</t>
+          <t>更新时间: 2026-10-13 17:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 17:34</t>
+          <t>更新时间: 2026-10-13 19:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 19:27</t>
+          <t>更新时间: 2026-10-14 10:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 10:19</t>
+          <t>更新时间: 2026-10-14 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 12:51</t>
+          <t>更新时间: 2026-10-14 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:36</t>
+          <t>更新时间: 2026-10-14 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 15:48</t>
+          <t>更新时间: 2026-10-14 17:19</t>
         </is>
       </c>
     </row>
